--- a/reports/informe_loop.xlsx
+++ b/reports/informe_loop.xlsx
@@ -481,17 +481,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11-17-24-26-38</t>
+          <t>9-14-22-28-29</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0645</v>
+        <v>1.1257</v>
       </c>
       <c r="F2" t="n">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,17 +512,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10-14-22-28-29</t>
+          <t>11-17-24-26-38</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0468</v>
+        <v>1.1147</v>
       </c>
       <c r="F3" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,7 +550,7 @@
         <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>1.987</v>
+        <v>1.1376</v>
       </c>
       <c r="F4" t="n">
         <v>121</v>
@@ -581,7 +581,7 @@
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5728</v>
+        <v>0.9319</v>
       </c>
       <c r="F5" t="n">
         <v>115</v>
@@ -605,15 +605,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5-12-16-26-37</t>
+          <t>10-11-25-26-29</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>1.6693</v>
+        <v>1.0222</v>
       </c>
       <c r="F6" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -634,15 +634,15 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10-11-25-26-29</t>
+          <t>5-12-16-25-37</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>1.5708</v>
+        <v>0.8776</v>
       </c>
       <c r="F7" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11-18-27-31-34</t>
+          <t>9-14-21-27-28</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9-14-22-28-30</t>
+          <t>12-19-28-34-35</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8-15-20-27-28</t>
+          <t>4-11-32-38-43</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9-14-22-28-29</t>
+          <t>9-14-21-28-34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10-17-23-26-38</t>
+          <t>8-14-20-27-28</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -938,11 +938,11 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8-14-20-27-28</t>
+          <t>7-13-26-37-38</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8-14-22-28-29</t>
+          <t>8-14-21-27-28</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8-15-22-27-29</t>
+          <t>8-15-22-27-28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8-14-21-27-28</t>
+          <t>8-15-21-27-28</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8-14-21-28-29</t>
+          <t>9-14-21-28-29</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>11-17-25-26-39</t>
+          <t>11-17-24-26-38</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11-17-25-26-38</t>
+          <t>9-14-22-28-29</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10-17-23-26-38</t>
+          <t>8-14-21-27-28</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>11-17-25-26-38</t>
+          <t>9-14-22-28-29</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9-17-25-26-38</t>
+          <t>8-14-21-28-34</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1358,11 +1358,11 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8-14-21-27-29</t>
+          <t>8-14-21-27-28</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8-14-22-28-29</t>
+          <t>8-14-21-28-29</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8-14-21-26-28</t>
+          <t>8-14-21-27-28</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>7-14-22-27-28</t>
+          <t>8-14-22-27-28</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8-14-22-28-29</t>
+          <t>8-14-21-27-28</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>6-11-25-37-38</t>
+          <t>8-15-22-25-38</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7-13-19-26-27</t>
+          <t>8-13-19-26-28</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4-9-31-38-43</t>
+          <t>9-17-25-30-32</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8-14-23-25-39</t>
+          <t>8-15-22-25-39</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>9-17-25-31-32</t>
+          <t>4-9-31-38-42</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1778,11 +1778,11 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8-15-23-25-38</t>
+          <t>6-11-25-37-38</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5-8-13-35-37</t>
+          <t>5-8-14-35-36</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4-9-31-38-43</t>
+          <t>4-9-30-38-43</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4-9-29-38-43</t>
+          <t>4-9-29-37-42</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1918,11 +1918,11 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3-8-29-38-43</t>
+          <t>4-9-29-38-42</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4-9-28-38-43</t>
+          <t>4-9-28-38-42</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4-8-28-38-43</t>
+          <t>4-9-28-38-43</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3-8-28-38-43</t>
+          <t>6-14-19-35-36</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4-9-28-38-43</t>
+          <t>4-9-28-38-42</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>6-12-17-25-31</t>
+          <t>4-9-29-38-43</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5-13-18-35-36</t>
+          <t>4-9-28-38-42</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3-8-28-38-43</t>
+          <t>5-14-19-35-36</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3-8-29-38-43</t>
+          <t>4-9-29-38-42</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3-8-29-38-43</t>
+          <t>4-9-29-38-42</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>4-8-28-38-43</t>
+          <t>5-14-19-35-36</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5-6-14-26-40</t>
+          <t>4-9-28-38-42</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>5-12-16-26-37</t>
+          <t>3-8-21-31-36</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>5-12-16-25-37</t>
+          <t>5-11-16-23-37</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3-8-22-31-36</t>
+          <t>5-13-26-27-38</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>5-11-16-25-38</t>
+          <t>3-8-22-31-36</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3-8-22-31-36</t>
+          <t>5-11-15-24-37</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>5-11-16-25-38</t>
+          <t>5-10-15-25-38</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1-5-12-27-38</t>
+          <t>5-10-14-23-38</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5-12-16-17-38</t>
+          <t>5-11-15-16-38</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>5-11-16-25-38</t>
+          <t>5-11-15-25-38</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>5-11-16-26-37</t>
+          <t>10-11-25-26-29</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>6-11-16-24-37</t>
+          <t>10-11-23-26-28</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3-8-23-31-37</t>
+          <t>10-11-25-26-29</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>5-11-16-25-38</t>
+          <t>10-22-25-26-29</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>9-10-25-26-29</t>
+          <t>5-6-7-31-37</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>9-10-25-26-29</t>
+          <t>3-8-22-30-37</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>5-11-15-25-38</t>
+          <t>10-21-25-26-29</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>5-11-15-16-37</t>
+          <t>3-8-23-31-37</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>5-11-15-16-38</t>
+          <t>5-11-15-25-38</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>5-12-17-25-38</t>
+          <t>10-11-25-26-29</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3248,11 +3248,11 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>10-11-25-26-29</t>
+          <t>3-8-23-30-37</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>3-8-22-31-37</t>
+          <t>3-8-22-30-37</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3318,11 +3318,11 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>5-11-16-25-38</t>
+          <t>10-11-25-26-29</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>10-22-25-26-29</t>
+          <t>10-11-23-25-28</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>10-11-26-27-29</t>
+          <t>10-11-23-26-29</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10-12-25-26-29</t>
+          <t>10-11-25-26-29</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>6-12-16-25-37</t>
+          <t>10-11-25-26-29</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>6-12-16-25-37</t>
+          <t>10-11-25-26-29</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3668,11 +3668,11 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>10-12-25-26-29</t>
+          <t>10-11-25-26-29</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>7-13-18-25-37</t>
+          <t>3-10-23-33-37</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>10-11-22-25-27</t>
+          <t>10-11-24-25-27</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>6-12-15-23-37</t>
+          <t>10-11-23-25-27</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3878,11 +3878,11 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>6-12-16-23-37</t>
+          <t>7-12-16-23-37</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>3-10-22-29-36</t>
+          <t>10-11-23-25-27</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>10-11-22-23-27</t>
+          <t>6-11-15-23-37</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>11-12-23-24-27</t>
+          <t>11-21-23-24-27</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>11-22-23-25-27</t>
+          <t>3-10-21-29-36</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4123,11 +4123,11 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>11-21-23-24-27</t>
+          <t>7-11-15-24-37</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4258,7 +4258,7 @@
         <v>0.1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="3">
@@ -4277,7 +4277,7 @@
         <v>0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="4">
@@ -4287,16 +4287,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
         <v>50</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
     </row>
   </sheetData>
@@ -4310,7 +4310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4897,6 +4897,198 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:30:34</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D25" t="n">
+        <v>100</v>
+      </c>
+      <c r="E25" t="n">
+        <v>8</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>{'M1_freq': -0.079, 'M3_gap': -0.066, 'M8_tendencia': -0.085, 'M9_markov': -0.072}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:31:16</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D26" t="n">
+        <v>100</v>
+      </c>
+      <c r="E26" t="n">
+        <v>12</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>{'M1_freq': -0.071, 'M3_gap': -0.059, 'M8_tendencia': -0.077, 'M9_markov': -0.065}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:33:21</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E27" t="n">
+        <v>12</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>{'M1_freq': -0.064, 'M3_gap': -0.053, 'M8_tendencia': -0.069, 'M9_markov': -0.059}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:33:52</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D28" t="n">
+        <v>100</v>
+      </c>
+      <c r="E28" t="n">
+        <v>12</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>{'M1_freq': -0.057, 'M3_gap': -0.048, 'M8_tendencia': -0.062, 'M9_markov': -0.053}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:34:15</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D29" t="n">
+        <v>100</v>
+      </c>
+      <c r="E29" t="n">
+        <v>14</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>{'M1_freq': -0.052, 'M3_gap': -0.043, 'M8_tendencia': -0.056, 'M9_markov': -0.047}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>4</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:34:56</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D30" t="n">
+        <v>100</v>
+      </c>
+      <c r="E30" t="n">
+        <v>14</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>{'M1_freq': -0.046, 'M3_gap': -0.039, 'M8_tendencia': -0.05, 'M9_markov': -0.043}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>5</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:35:20</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E31" t="n">
+        <v>12</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>{'M1_freq': -0.042, 'M3_gap': -0.035, 'M8_tendencia': -0.045, 'M9_markov': -0.038}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:35:47</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D32" t="n">
+        <v>100</v>
+      </c>
+      <c r="E32" t="n">
+        <v>12</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>{'M1_freq': -0.038, 'M3_gap': -0.031, 'M8_tendencia': -0.041, 'M9_markov': -0.035}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/informe_loop.xlsx
+++ b/reports/informe_loop.xlsx
@@ -481,17 +481,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9-14-22-28-29</t>
+          <t>9-14-21-28-29</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1257</v>
+        <v>0.8666</v>
       </c>
       <c r="F2" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -519,7 +519,7 @@
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1147</v>
+        <v>0.7795</v>
       </c>
       <c r="F3" t="n">
         <v>116</v>
@@ -550,7 +550,7 @@
         <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1376</v>
+        <v>0.8375</v>
       </c>
       <c r="F4" t="n">
         <v>121</v>
@@ -574,17 +574,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8-9-22-37-39</t>
+          <t>8-9-21-36-39</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9319</v>
+        <v>0.5863</v>
       </c>
       <c r="F5" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -605,15 +605,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10-11-25-26-29</t>
+          <t>3-8-21-30-36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>1.0222</v>
+        <v>0.797</v>
       </c>
       <c r="F6" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -634,15 +634,15 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5-12-16-25-37</t>
+          <t>10-21-25-26-28</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>0.8776</v>
+        <v>0.6974</v>
       </c>
       <c r="F7" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9-14-21-27-28</t>
+          <t>9-14-21-28-34</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12-19-28-34-35</t>
+          <t>9-14-22-28-29</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4-11-32-38-43</t>
+          <t>9-14-21-27-28</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8-14-20-27-28</t>
+          <t>4-11-31-37-42</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9-14-21-28-34</t>
+          <t>9-14-21-27-28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12-19-28-34-35</t>
+          <t>9-14-21-28-29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -903,11 +903,11 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11-17-24-26-38</t>
+          <t>9-14-21-27-28</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8-15-21-27-28</t>
+          <t>9-15-21-27-28</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>9-14-21-28-29</t>
+          <t>11-12-17-23-38</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>11-17-24-26-38</t>
+          <t>9-15-21-28-29</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1183,11 +1183,11 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>9-14-22-28-29</t>
+          <t>9-14-21-28-29</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>9-14-22-28-29</t>
+          <t>9-14-21-28-33</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8-14-22-28-29</t>
+          <t>9-14-21-28-33</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8-14-21-28-29</t>
+          <t>8-14-21-28-34</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8-14-22-28-29</t>
+          <t>8-14-21-28-34</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1463,11 +1463,11 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8-14-22-27-28</t>
+          <t>8-14-21-27-28</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8-15-22-25-38</t>
+          <t>9-15-22-25-38</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>9-17-25-30-32</t>
+          <t>7-13-19-26-28</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8-15-22-25-39</t>
+          <t>8-13-19-26-27</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4-9-31-38-42</t>
+          <t>6-14-21-35-36</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6-11-25-37-38</t>
+          <t>4-9-30-37-42</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1813,11 +1813,11 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5-8-14-35-36</t>
+          <t>4-9-29-38-42</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4-9-30-38-43</t>
+          <t>4-13-19-27-37</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4-9-28-38-42</t>
+          <t>6-9-14-35-36</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4-9-28-38-43</t>
+          <t>6-9-14-35-37</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>6-14-19-35-36</t>
+          <t>4-9-28-38-42</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4-9-29-38-43</t>
+          <t>6-9-14-35-36</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>5-14-19-35-36</t>
+          <t>4-9-29-38-42</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4-9-29-38-42</t>
+          <t>9-15-21-23-38</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3-8-28-38-43</t>
+          <t>4-9-29-38-42</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2268,11 +2268,11 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5-14-19-35-36</t>
+          <t>4-9-28-38-42</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>10-11-25-26-29</t>
+          <t>10-21-25-26-29</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3-8-21-31-36</t>
+          <t>3-8-21-30-36</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>5-11-16-23-37</t>
+          <t>5-11-15-24-37</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>5-13-26-27-38</t>
+          <t>3-12-22-35-38</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3-8-22-31-36</t>
+          <t>5-11-15-24-37</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>5-11-15-24-37</t>
+          <t>3-8-22-23-36</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>5-10-14-23-38</t>
+          <t>8-10-23-25-28</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5-11-15-16-38</t>
+          <t>5-11-15-25-38</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>5-11-15-25-38</t>
+          <t>10-22-25-26-29</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2863,11 +2863,11 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>10-11-25-26-29</t>
+          <t>6-11-15-25-38</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>10-11-23-26-28</t>
+          <t>6-11-15-23-38</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>10-11-25-26-29</t>
+          <t>6-11-15-16-38</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2968,11 +2968,11 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10-22-25-26-29</t>
+          <t>1-6-26-27-38</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3003,11 +3003,11 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>5-6-7-31-37</t>
+          <t>3-8-23-30-36</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>3-8-23-31-37</t>
+          <t>3-8-22-30-37</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>5-11-15-25-38</t>
+          <t>10-21-25-26-29</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>10-11-25-26-29</t>
+          <t>10-22-25-26-29</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>3-8-23-30-37</t>
+          <t>10-11-25-26-28</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>3-8-22-30-37</t>
+          <t>5-11-15-24-37</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3318,11 +3318,11 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>10-11-23-25-28</t>
+          <t>10-11-24-25-28</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3423,11 +3423,11 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>10-11-25-26-29</t>
+          <t>10-11-25-26-28</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>10-11-23-26-29</t>
+          <t>10-11-25-26-29</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>10-11-25-26-29</t>
+          <t>10-11-25-26-28</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>10-11-25-26-29</t>
+          <t>10-11-23-25-28</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>3-10-23-33-37</t>
+          <t>11-23-25-26-29</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>7-12-16-23-37</t>
+          <t>10-11-24-25-27</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>10-11-23-25-27</t>
+          <t>10-11-24-25-27</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>10-11-23-24-27</t>
+          <t>6-11-15-23-37</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4018,11 +4018,11 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>3-10-21-29-36</t>
+          <t>7-11-15-24-37</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4123,11 +4123,11 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>10-11-22-23-26</t>
+          <t>10-11-21-23-26</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
         <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="E2" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="3">
@@ -4268,16 +4268,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
         <v>50</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="E3" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="4">
@@ -4287,16 +4287,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
         <v>50</v>
       </c>
       <c r="D4" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="E4" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
     </row>
   </sheetData>
@@ -4310,7 +4310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5089,6 +5089,198 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>7</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:36:15</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D33" t="n">
+        <v>100</v>
+      </c>
+      <c r="E33" t="n">
+        <v>11</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>{'M1_freq': -0.034, 'M3_gap': -0.028, 'M8_tendencia': -0.037, 'M9_markov': -0.031}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>8</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:36:47</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D34" t="n">
+        <v>100</v>
+      </c>
+      <c r="E34" t="n">
+        <v>11</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>{'M1_freq': -0.03, 'M3_gap': -0.025, 'M8_tendencia': -0.033, 'M9_markov': -0.028}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>9</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:37:15</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D35" t="n">
+        <v>100</v>
+      </c>
+      <c r="E35" t="n">
+        <v>11</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>{'M1_freq': -0.027, 'M3_gap': -0.023, 'M8_tendencia': -0.03, 'M9_markov': -0.025}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>10</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:37:51</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D36" t="n">
+        <v>100</v>
+      </c>
+      <c r="E36" t="n">
+        <v>12</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:38:55</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D37" t="n">
+        <v>100</v>
+      </c>
+      <c r="E37" t="n">
+        <v>11</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>{'M1_freq': -0.027, 'M3_gap': -0.023, 'M8_tendencia': -0.03, 'M9_markov': -0.025}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:39:23</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D38" t="n">
+        <v>100</v>
+      </c>
+      <c r="E38" t="n">
+        <v>12</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>{'M1_freq': -0.025, 'M3_gap': -0.021, 'M8_tendencia': -0.027, 'M9_markov': -0.023}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>3</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:39:49</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D39" t="n">
+        <v>100</v>
+      </c>
+      <c r="E39" t="n">
+        <v>12</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>{'M1_freq': -0.022, 'M3_gap': -0.018, 'M8_tendencia': -0.024, 'M9_markov': -0.02}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:40:50</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D40" t="n">
+        <v>100</v>
+      </c>
+      <c r="E40" t="n">
+        <v>14</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>{'M1_freq': -0.02, 'M3_gap': -0.017, 'M8_tendencia': -0.022, 'M9_markov': -0.018}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/informe_loop.xlsx
+++ b/reports/informe_loop.xlsx
@@ -481,21 +481,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9-14-21-28-29</t>
+          <t>4-8-15-30-37</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8666</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -512,21 +512,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11-17-24-26-38</t>
+          <t>6-18-22-28-35</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7795</v>
+        <v>0.7148</v>
       </c>
       <c r="F3" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -543,21 +543,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15-18-22-28-38</t>
+          <t>4-7-20-38-42</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8375</v>
+        <v>0.5812</v>
       </c>
       <c r="F4" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8-9-21-36-39</t>
+          <t>5-6-23-29-32</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5863</v>
+        <v>0.3874</v>
       </c>
       <c r="F5" t="n">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -605,19 +605,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3-8-21-30-36</t>
+          <t>3-16-25-32-38</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>0.797</v>
+        <v>0.6065</v>
       </c>
       <c r="F6" t="n">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -634,19 +634,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10-21-25-26-28</t>
+          <t>11-14-22-26-27</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>0.6974</v>
+        <v>0.5747</v>
       </c>
       <c r="F7" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13 de Julio de 2026</t>
+          <t>15 de Julio de 2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -719,16 +719,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9-14-21-28-34</t>
+          <t>6-20-22-28-35</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8-11-21-32-38</t>
+          <t>2-4-8-12-24</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13 de Julio de 2026</t>
+          <t>15 de Julio de 2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -754,20 +754,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9-14-22-28-29</t>
+          <t>7-20-22-28-35</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10-11-15-21-34</t>
+          <t>10-22-27-30-35</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11 de Julio de 2026</t>
+          <t>13 de Julio de 2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -789,16 +789,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9-14-21-27-28</t>
+          <t>7-19-22-28-35</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3-22-28-32-34</t>
+          <t>8-11-21-32-38</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11 de Julio de 2026</t>
+          <t>13 de Julio de 2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -824,16 +824,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4-11-31-37-42</t>
+          <t>9-14-17-32-35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>29-35-38-41-42</t>
+          <t>10-11-15-21-34</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8 de Julio de 2026</t>
+          <t>11 de Julio de 2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9-14-21-27-28</t>
+          <t>10-14-15-35-37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11-15-20-24-30</t>
+          <t>3-22-28-32-34</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -884,7 +884,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8 de Julio de 2026</t>
+          <t>11 de Julio de 2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9-14-21-28-29</t>
+          <t>4-12-22-28-37</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4-12-26-35-37</t>
+          <t>29-35-38-41-42</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6 de Julio de 2026</t>
+          <t>8 de Julio de 2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -929,20 +929,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8-14-20-27-28</t>
+          <t>10-14-15-35-37</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2-12-16-27-28</t>
+          <t>11-15-20-24-30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6 de Julio de 2026</t>
+          <t>8 de Julio de 2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -964,16 +964,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7-13-26-37-38</t>
+          <t>9-14-17-32-35</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>14-17-31-42-43</t>
+          <t>4-12-26-35-37</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4 de Julio de 2026</t>
+          <t>6 de Julio de 2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -999,16 +999,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8-14-21-27-28</t>
+          <t>10-14-15-35-38</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9-14-40-42-43</t>
+          <t>2-12-16-27-28</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4 de Julio de 2026</t>
+          <t>6 de Julio de 2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1034,16 +1034,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9-14-21-27-28</t>
+          <t>3-13-22-28-37</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3-4-14-26-41</t>
+          <t>14-17-31-42-43</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1 de Julio de 2026</t>
+          <t>4 de Julio de 2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1069,16 +1069,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8-15-22-27-28</t>
+          <t>8-14-16-31-35</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3-12-13-17-37</t>
+          <t>9-14-40-42-43</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1 de Julio de 2026</t>
+          <t>4 de Julio de 2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1104,16 +1104,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>9-15-21-27-28</t>
+          <t>11-14-15-34-37</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3-14-26-34-35</t>
+          <t>3-4-14-26-41</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>29 de Junio de 2026</t>
+          <t>1 de Julio de 2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>11-12-17-23-38</t>
+          <t>6-19-22-28-35</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10-15-22-24-30</t>
+          <t>3-12-13-17-37</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>29 de Junio de 2026</t>
+          <t>1 de Julio de 2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>9-15-21-28-29</t>
+          <t>9-14-17-31-35</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>15-21-25-31-35</t>
+          <t>3-14-26-34-35</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>27 de Junio de 2026</t>
+          <t>29 de Junio de 2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1209,16 +1209,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>9-14-21-28-29</t>
+          <t>9-14-17-31-35</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>15-23-29-33-41</t>
+          <t>10-15-22-24-30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>27 de Junio de 2026</t>
+          <t>29 de Junio de 2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1244,20 +1244,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8-14-21-27-28</t>
+          <t>11-14-15-35-37</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13-17-18-30-35</t>
+          <t>15-21-25-31-35</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>24 de Junio de 2026</t>
+          <t>27 de Junio de 2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1279,12 +1279,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>9-14-21-28-33</t>
+          <t>11-14-15-35-37</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12-14-30-36-43</t>
+          <t>15-23-29-33-41</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>24 de Junio de 2026</t>
+          <t>27 de Junio de 2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1314,16 +1314,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9-14-21-28-33</t>
+          <t>7-19-22-28-35</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>8-17-31-36-41</t>
+          <t>13-17-18-30-35</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>22 de Junio de 2026</t>
+          <t>24 de Junio de 2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1349,20 +1349,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8-14-21-28-34</t>
+          <t>7-19-22-28-35</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8-12-16-28-33</t>
+          <t>12-14-30-36-43</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>22 de Junio de 2026</t>
+          <t>24 de Junio de 2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1384,16 +1384,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8-14-21-27-28</t>
+          <t>7-19-22-28-35</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4-10-20-27-36</t>
+          <t>8-17-31-36-41</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20 de Junio de 2026</t>
+          <t>22 de Junio de 2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1419,20 +1419,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8-14-21-28-34</t>
+          <t>4-8-16-31-37</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>31-34-37-38-43</t>
+          <t>8-12-16-28-33</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20 de Junio de 2026</t>
+          <t>22 de Junio de 2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8-14-21-28-34</t>
+          <t>4-8-15-31-37</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>8-17-26-29-32</t>
+          <t>4-10-20-27-36</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17 de Junio de 2026</t>
+          <t>20 de Junio de 2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1489,16 +1489,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8-14-21-27-28</t>
+          <t>10-13-14-35-37</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16-20-34-37-39</t>
+          <t>31-34-37-38-43</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17 de Junio de 2026</t>
+          <t>20 de Junio de 2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1524,12 +1524,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8-14-21-27-28</t>
+          <t>6-19-22-28-35</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>7-12-19-34-35</t>
+          <t>8-17-26-29-32</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15 de Junio de 2026</t>
+          <t>17 de Junio de 2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1559,16 +1559,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8-14-21-27-28</t>
+          <t>8-13-16-31-35</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4-13-16-22-31</t>
+          <t>16-20-34-37-39</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15 de Junio de 2026</t>
+          <t>17 de Junio de 2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8-14-21-27-28</t>
+          <t>4-8-15-31-37</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>18-24-32-37-39</t>
+          <t>7-12-19-34-35</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13 de Junio de 2026</t>
+          <t>15 de Junio de 2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1629,20 +1629,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>9-15-22-25-38</t>
+          <t>4-8-15-31-37</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>13-18-26-28-29</t>
+          <t>4-13-16-22-31</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13 de Junio de 2026</t>
+          <t>15 de Junio de 2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1664,12 +1664,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8-13-19-26-28</t>
+          <t>6-19-22-28-35</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>22-35-37-38-42</t>
+          <t>18-24-32-37-39</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10 de Junio de 2026</t>
+          <t>13 de Junio de 2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1699,16 +1699,16 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7-13-19-26-28</t>
+          <t>9-13-14-35-37</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3-5-17-18-27</t>
+          <t>13-18-26-28-29</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10 de Junio de 2026</t>
+          <t>13 de Junio de 2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1734,16 +1734,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8-13-19-26-27</t>
+          <t>8-13-15-30-35</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7-14-22-35-41</t>
+          <t>22-35-37-38-42</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8 de Junio de 2026</t>
+          <t>10 de Junio de 2026</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1769,16 +1769,16 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>6-14-21-35-36</t>
+          <t>8-13-15-30-35</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6-8-9-32-40</t>
+          <t>3-5-17-18-27</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8 de Junio de 2026</t>
+          <t>10 de Junio de 2026</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1804,20 +1804,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4-9-30-37-42</t>
+          <t>8-13-15-29-35</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>14-26-30-37-39</t>
+          <t>7-14-22-35-41</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6 de Junio de 2026</t>
+          <t>8 de Junio de 2026</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1839,20 +1839,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>4-9-29-38-42</t>
+          <t>9-13-14-32-37</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>5-15-19-28-32</t>
+          <t>6-8-9-32-40</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6 de Junio de 2026</t>
+          <t>8 de Junio de 2026</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1874,16 +1874,16 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4-13-19-27-37</t>
+          <t>9-13-14-32-36</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>7-11-25-32-36</t>
+          <t>14-26-30-37-39</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3 de Junio de 2026</t>
+          <t>6 de Junio de 2026</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4-9-29-37-42</t>
+          <t>9-13-32-35-37</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>26-29-35-38-41</t>
+          <t>5-15-19-28-32</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3 de Junio de 2026</t>
+          <t>6 de Junio de 2026</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4-9-29-38-42</t>
+          <t>9-13-14-32-37</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4-12-13-31-35</t>
+          <t>7-11-25-32-36</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1 de Junio de 2026</t>
+          <t>3 de Junio de 2026</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1979,12 +1979,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>6-9-14-35-36</t>
+          <t>9-13-14-32-36</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4-22-30-31-39</t>
+          <t>26-29-35-38-41</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1 de Junio de 2026</t>
+          <t>3 de Junio de 2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>6-9-14-35-37</t>
+          <t>9-13-14-32-37</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>12-19-33-35-41</t>
+          <t>4-12-13-31-35</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>30 de Mayo de 2026</t>
+          <t>1 de Junio de 2026</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4-9-28-38-42</t>
+          <t>9-13-14-32-37</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2-8-11-25-26</t>
+          <t>4-22-30-31-39</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>30 de Mayo de 2026</t>
+          <t>1 de Junio de 2026</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2084,16 +2084,16 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4-9-28-38-42</t>
+          <t>9-13-14-32-37</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>8-14-23-34-38</t>
+          <t>12-19-33-35-41</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>27 de Mayo de 2026</t>
+          <t>30 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2119,16 +2119,16 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>6-9-14-35-36</t>
+          <t>9-13-14-32-37</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>7-14-20-23-40</t>
+          <t>2-8-11-25-26</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>27 de Mayo de 2026</t>
+          <t>30 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2154,16 +2154,16 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4-9-28-38-42</t>
+          <t>9-13-14-32-37</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>11-24-26-31-37</t>
+          <t>8-14-23-34-38</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>25 de Mayo de 2026</t>
+          <t>27 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>4-9-29-38-42</t>
+          <t>9-13-14-32-37</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>12-14-37-38-39</t>
+          <t>7-14-20-23-40</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>25 de Mayo de 2026</t>
+          <t>27 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2224,16 +2224,16 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>9-15-21-23-38</t>
+          <t>9-13-14-32-37</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6-13-20-32-42</t>
+          <t>11-24-26-31-37</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>23 de Mayo de 2026</t>
+          <t>25 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4-9-29-38-42</t>
+          <t>9-13-14-32-37</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>23-27-29-30-38</t>
+          <t>12-14-37-38-39</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>23 de Mayo de 2026</t>
+          <t>25 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2294,20 +2294,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4-9-29-38-42</t>
+          <t>9-13-14-32-37</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>12-16-25-27-37</t>
+          <t>6-13-20-32-42</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20 de Mayo de 2026</t>
+          <t>23 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2329,16 +2329,16 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>4-9-28-38-42</t>
+          <t>9-13-14-32-37</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1-28-32-33-35</t>
+          <t>23-27-29-30-38</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20 de Mayo de 2026</t>
+          <t>23 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2364,16 +2364,16 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>6-13-19-25-26</t>
+          <t>9-13-14-32-37</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>4-8-10-42-43</t>
+          <t>12-16-25-27-37</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>18 de Mayo de 2026</t>
+          <t>20 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2399,20 +2399,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>4-9-28-38-42</t>
+          <t>6-12-15-28-34</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>3-4-9-14-35</t>
+          <t>1-28-32-33-35</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>18 de Mayo de 2026</t>
+          <t>20 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>4-9-28-38-42</t>
+          <t>9-13-14-32-37</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>8-10-31-32-40</t>
+          <t>4-8-10-42-43</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>13 de Julio de 2026</t>
+          <t>14 de Julio de 2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>10-21-25-26-29</t>
+          <t>3-5-23-26-37</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>13-18-25-32-33</t>
+          <t>8-13-22-23-31</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>10 de Julio de 2026</t>
+          <t>13 de Julio de 2026</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2504,16 +2504,16 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3-8-21-30-36</t>
+          <t>3-5-24-26-37</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>16-18-32-34-36</t>
+          <t>13-18-25-32-33</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>9 de Julio de 2026</t>
+          <t>10 de Julio de 2026</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2539,12 +2539,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>5-11-15-24-37</t>
+          <t>11-15-22-26-27</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>4-13-26-34-39</t>
+          <t>16-18-32-34-36</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7 de Julio de 2026</t>
+          <t>9 de Julio de 2026</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2574,16 +2574,16 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3-12-22-35-38</t>
+          <t>3-19-21-26-27</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1-13-21-29-33</t>
+          <t>4-13-26-34-39</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>6 de Julio de 2026</t>
+          <t>7 de Julio de 2026</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>5-11-15-24-37</t>
+          <t>11-14-22-26-27</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2-17-26-28-30</t>
+          <t>1-13-21-29-33</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>3 de Julio de 2026</t>
+          <t>6 de Julio de 2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3-8-22-23-36</t>
+          <t>5-12-15-26-35</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>17-21-27-32-35</t>
+          <t>2-17-26-28-30</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2 de Julio de 2026</t>
+          <t>3 de Julio de 2026</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>5-10-15-25-38</t>
+          <t>5-12-15-25-35</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>10-12-16-19-32</t>
+          <t>17-21-27-32-35</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30 de Junio de 2026</t>
+          <t>2 de Julio de 2026</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2714,16 +2714,16 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>8-10-23-25-28</t>
+          <t>5-12-15-26-36</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>3-12-29-32-39</t>
+          <t>10-12-16-19-32</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>29 de Junio de 2026</t>
+          <t>30 de Junio de 2026</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5-11-15-25-38</t>
+          <t>5-11-14-26-36</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2-4-20-32-37</t>
+          <t>3-12-29-32-39</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>26 de Junio de 2026</t>
+          <t>29 de Junio de 2026</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2784,16 +2784,16 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>5-11-15-25-38</t>
+          <t>5-13-15-26-35</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>21-29-32-36-38</t>
+          <t>2-4-20-32-37</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>25 de Junio de 2026</t>
+          <t>26 de Junio de 2026</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2819,20 +2819,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>5-10-15-25-38</t>
+          <t>5-12-15-25-35</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>3-15-25-30-35</t>
+          <t>21-29-32-36-38</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>23 de Junio de 2026</t>
+          <t>25 de Junio de 2026</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2854,16 +2854,16 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>10-22-25-26-29</t>
+          <t>2-5-23-25-37</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>3-5-7-34-38</t>
+          <t>3-15-25-30-35</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>22 de Junio de 2026</t>
+          <t>23 de Junio de 2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2889,20 +2889,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>6-11-15-25-38</t>
+          <t>3-7-24-26-37</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>4-12-22-30-31</t>
+          <t>3-5-7-34-38</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>19 de Junio de 2026</t>
+          <t>22 de Junio de 2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>6-11-15-23-38</t>
+          <t>3-7-24-26-37</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2-22-35-36-37</t>
+          <t>4-12-22-30-31</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>18 de Junio de 2026</t>
+          <t>19 de Junio de 2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2959,20 +2959,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>6-11-15-16-38</t>
+          <t>3-19-21-26-27</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>6-7-11-14-21</t>
+          <t>2-22-35-36-37</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>16 de Junio de 2026</t>
+          <t>18 de Junio de 2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2994,20 +2994,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1-6-26-27-38</t>
+          <t>3-7-23-26-37</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>6-16-27-30-34</t>
+          <t>6-7-11-14-21</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>15 de Junio de 2026</t>
+          <t>16 de Junio de 2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3-8-23-30-36</t>
+          <t>3-7-24-26-37</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>11-16-28-33-38</t>
+          <t>6-16-27-30-34</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>12 de Junio de 2026</t>
+          <t>15 de Junio de 2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3064,16 +3064,16 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>3-8-22-30-37</t>
+          <t>12-15-22-26-27</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1-15-18-22-29</t>
+          <t>11-16-28-33-38</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>11 de Junio de 2026</t>
+          <t>12 de Junio de 2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3099,20 +3099,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10-21-25-26-29</t>
+          <t>12-15-22-26-27</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>19-23-26-27-36</t>
+          <t>1-15-18-22-29</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>9 de Junio de 2026</t>
+          <t>11 de Junio de 2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3134,20 +3134,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>3-8-22-30-37</t>
+          <t>12-15-22-26-27</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>6-10-14-17-27</t>
+          <t>19-23-26-27-36</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>8 de Junio de 2026</t>
+          <t>9 de Junio de 2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>10-21-25-26-29</t>
+          <t>12-15-22-26-27</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>9-13-18-29-32</t>
+          <t>6-10-14-17-27</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5 de Junio de 2026</t>
+          <t>8 de Junio de 2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>10-11-25-26-29</t>
+          <t>12-15-22-26-27</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2-14-22-36-38</t>
+          <t>9-13-18-29-32</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>4 de Junio de 2026</t>
+          <t>5 de Junio de 2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>10-22-25-26-29</t>
+          <t>8-10-13-17-35</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>3-7-12-17-36</t>
+          <t>2-14-22-36-38</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2 de Junio de 2026</t>
+          <t>4 de Junio de 2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3274,16 +3274,16 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>10-11-25-26-28</t>
+          <t>12-15-22-26-27</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>4-5-8-31-35</t>
+          <t>3-7-12-17-36</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1 de Junio de 2026</t>
+          <t>2 de Junio de 2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>5-11-15-24-37</t>
+          <t>12-15-22-26-27</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>4-8-23-26-30</t>
+          <t>4-5-8-31-35</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>29 de Mayo de 2026</t>
+          <t>1 de Junio de 2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3344,16 +3344,16 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>10-11-25-26-29</t>
+          <t>12-15-22-26-27</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>3-12-15-23-28</t>
+          <t>4-8-23-26-30</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>28 de Mayo de 2026</t>
+          <t>29 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3379,16 +3379,16 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>10-11-25-26-29</t>
+          <t>3-8-24-25-37</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>5-8-15-37-38</t>
+          <t>3-12-15-23-28</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>26 de Mayo de 2026</t>
+          <t>28 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3414,20 +3414,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>10-11-24-25-28</t>
+          <t>8-11-13-16-35</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>5-7-12-24-25</t>
+          <t>5-8-15-37-38</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>25 de Mayo de 2026</t>
+          <t>26 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>10-11-25-26-28</t>
+          <t>3-8-23-25-37</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2-8-23-28-34</t>
+          <t>5-7-12-24-25</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>22 de Mayo de 2026</t>
+          <t>25 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>10-11-25-26-29</t>
+          <t>12-15-22-26-27</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1-18-19-22-35</t>
+          <t>2-8-23-28-34</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>21 de Mayo de 2026</t>
+          <t>22 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10-11-25-26-29</t>
+          <t>8-11-12-33-37</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>3-5-31-32-38</t>
+          <t>1-18-19-22-35</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>19 de Mayo de 2026</t>
+          <t>21 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3554,16 +3554,16 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>10-11-25-26-29</t>
+          <t>3-8-24-26-37</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>8-14-19-21-38</t>
+          <t>3-5-31-32-38</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>18 de Mayo de 2026</t>
+          <t>19 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>10-11-25-26-28</t>
+          <t>3-7-24-26-37</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>5-9-12-31-34</t>
+          <t>8-14-19-21-38</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15 de Mayo de 2026</t>
+          <t>18 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3624,16 +3624,16 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>10-11-25-26-29</t>
+          <t>12-15-23-27-28</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>9-21-23-34-35</t>
+          <t>5-9-12-31-34</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>14 de Mayo de 2026</t>
+          <t>15 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3659,20 +3659,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10-11-25-26-29</t>
+          <t>8-11-12-17-35</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>11-20-25-28-29</t>
+          <t>9-21-23-34-35</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>12 de Mayo de 2026</t>
+          <t>14 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3694,16 +3694,16 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>10-11-25-26-29</t>
+          <t>1-8-16-29-39</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1-6-8-27-35</t>
+          <t>11-20-25-28-29</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>11 de Mayo de 2026</t>
+          <t>12 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3729,20 +3729,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>10-11-23-25-28</t>
+          <t>1-8-16-29-39</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>3-7-8-35-38</t>
+          <t>1-6-8-27-35</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>8 de Mayo de 2026</t>
+          <t>11 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>11-23-25-26-29</t>
+          <t>12-15-22-26-27</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1-2-13-28-31</t>
+          <t>3-7-8-35-38</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>7 de Mayo de 2026</t>
+          <t>8 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3799,20 +3799,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>10-11-25-26-29</t>
+          <t>3-9-13-26-33</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>25-29-34-37-39</t>
+          <t>1-2-13-28-31</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5 de Mayo de 2026</t>
+          <t>7 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>10-11-24-25-27</t>
+          <t>9-10-11-33-37</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>4-24-33-35-37</t>
+          <t>25-29-34-37-39</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>4 de Mayo de 2026</t>
+          <t>5 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3869,16 +3869,16 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>10-11-23-25-27</t>
+          <t>3-16-25-33-37</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>5-10-20-25-27</t>
+          <t>4-24-33-35-37</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1 de Mayo de 2026</t>
+          <t>4 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3904,12 +3904,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>10-11-24-25-27</t>
+          <t>3-16-24-33-37</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>3-13-15-33-37</t>
+          <t>5-10-20-25-27</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>30 de Abril de 2026</t>
+          <t>1 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3939,16 +3939,16 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>10-11-24-25-27</t>
+          <t>8-11-13-17-35</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>13-20-32-35-36</t>
+          <t>3-13-15-33-37</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>28 de Abril de 2026</t>
+          <t>30 de Abril de 2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3974,16 +3974,16 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>6-11-15-23-37</t>
+          <t>3-8-23-25-37</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>8-16-26-37-38</t>
+          <t>13-20-32-35-36</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>27 de Abril de 2026</t>
+          <t>28 de Abril de 2026</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4009,20 +4009,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>6-11-15-23-37</t>
+          <t>3-8-23-24-36</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>6-15-17-25-38</t>
+          <t>8-16-26-37-38</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>24 de Abril de 2026</t>
+          <t>27 de Abril de 2026</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4044,16 +4044,16 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>6-11-15-23-37</t>
+          <t>3-8-23-25-36</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>20-25-28-32-35</t>
+          <t>6-15-17-25-38</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>23 de Abril de 2026</t>
+          <t>24 de Abril de 2026</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>11-21-23-24-27</t>
+          <t>8-11-12-17-34</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>3-4-8-10-30</t>
+          <t>20-25-28-32-35</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>21 de Abril de 2026</t>
+          <t>23 de Abril de 2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>7-11-15-24-37</t>
+          <t>12-15-22-26-31</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>3-4-21-23-29</t>
+          <t>3-4-8-10-30</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>20 de Abril de 2026</t>
+          <t>21 de Abril de 2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4149,12 +4149,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>10-11-21-23-26</t>
+          <t>12-15-22-26-31</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>4-12-27-30-35</t>
+          <t>3-4-21-23-29</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>17 de Abril de 2026</t>
+          <t>20 de Abril de 2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4184,16 +4184,16 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>7-11-15-24-37</t>
+          <t>13-15-16-26-39</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>5-23-25-33-37</t>
+          <t>4-12-27-30-35</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
         <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="3">
@@ -4268,16 +4268,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
         <v>50</v>
       </c>
       <c r="D3" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="4">
@@ -4287,16 +4287,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
         <v>50</v>
       </c>
       <c r="D4" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
     </row>
   </sheetData>
@@ -4310,7 +4310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5281,6 +5281,366 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:41:23</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>100</v>
+      </c>
+      <c r="E41" t="n">
+        <v>10</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>{'M1_freq': -0.018, 'M3_gap': -0.015, 'M8_tendencia': -0.019, 'M9_markov': -0.016}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:41:55</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D42" t="n">
+        <v>100</v>
+      </c>
+      <c r="E42" t="n">
+        <v>13</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>{'M1_freq': -0.016, 'M3_gap': -0.013, 'M8_tendencia': -0.018, 'M9_markov': -0.015}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>4</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:42:20</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D43" t="n">
+        <v>100</v>
+      </c>
+      <c r="E43" t="n">
+        <v>12</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>{'M1_freq': -0.015, 'M3_gap': -0.012, 'M8_tendencia': -0.016, 'M9_markov': -0.013}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>5</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:42:44</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>100</v>
+      </c>
+      <c r="E44" t="n">
+        <v>10</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>{'M1_freq': -0.013, 'M3_gap': -0.01, 'M8_tendencia': -0.014, 'M9_markov': -0.012}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>6</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:43:05</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D45" t="n">
+        <v>100</v>
+      </c>
+      <c r="E45" t="n">
+        <v>12</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>{'M1_freq': -0.012, 'M8_tendencia': -0.013, 'M9_markov': -0.009}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>7</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:43:27</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>100</v>
+      </c>
+      <c r="E46" t="n">
+        <v>10</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>{'M1_freq': -0.006, 'M8_tendencia': -0.011}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>8</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:43:50</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D47" t="n">
+        <v>100</v>
+      </c>
+      <c r="E47" t="n">
+        <v>12</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>{'M8_tendencia': -0.004}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>9</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:44:12</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D48" t="n">
+        <v>100</v>
+      </c>
+      <c r="E48" t="n">
+        <v>12</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>10</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:44:39</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D49" t="n">
+        <v>100</v>
+      </c>
+      <c r="E49" t="n">
+        <v>12</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:40:02</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D50" t="n">
+        <v>100</v>
+      </c>
+      <c r="E50" t="n">
+        <v>13</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:41:11</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D51" t="n">
+        <v>100</v>
+      </c>
+      <c r="E51" t="n">
+        <v>13</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>3</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:41:34</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D52" t="n">
+        <v>100</v>
+      </c>
+      <c r="E52" t="n">
+        <v>13</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>4</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:41:56</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D53" t="n">
+        <v>100</v>
+      </c>
+      <c r="E53" t="n">
+        <v>13</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>5</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:42:23</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D54" t="n">
+        <v>100</v>
+      </c>
+      <c r="E54" t="n">
+        <v>13</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>6</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:42:48</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D55" t="n">
+        <v>100</v>
+      </c>
+      <c r="E55" t="n">
+        <v>13</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/informe_loop.xlsx
+++ b/reports/informe_loop.xlsx
@@ -481,21 +481,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4-8-15-30-37</t>
+          <t>4-13-33-34-37</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.7399</v>
       </c>
       <c r="F2" t="n">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -512,21 +512,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6-18-22-28-35</t>
+          <t>3-8-22-39-41</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7148</v>
+        <v>0.6512</v>
       </c>
       <c r="F3" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -543,21 +543,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4-7-20-38-42</t>
+          <t>4-9-18-33-39</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5812</v>
+        <v>0.6714</v>
       </c>
       <c r="F4" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5-6-23-29-32</t>
+          <t>6-12-13-22-39</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3874</v>
+        <v>0.5888</v>
       </c>
       <c r="F5" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -605,19 +605,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3-16-25-32-38</t>
+          <t>3-15-26-29-36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>0.6065</v>
+        <v>0.7923</v>
       </c>
       <c r="F6" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -634,19 +634,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11-14-22-26-27</t>
+          <t>5-7-20-24-31</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>0.5747</v>
+        <v>0.4318</v>
       </c>
       <c r="F7" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15 de Julio de 2026</t>
+          <t>20 de Julio de 2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-20-22-28-35</t>
+          <t>4-13-34-35-38</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2-4-8-12-24</t>
+          <t>3-22-23-25-37</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -744,7 +744,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15 de Julio de 2026</t>
+          <t>20 de Julio de 2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -754,20 +754,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7-20-22-28-35</t>
+          <t>8-14-16-32-39</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10-22-27-30-35</t>
+          <t>3-10-11-23-33</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13 de Julio de 2026</t>
+          <t>18 de Julio de 2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -789,16 +789,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7-19-22-28-35</t>
+          <t>8-14-15-32-38</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8-11-21-32-38</t>
+          <t>8-17-19-24-26</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13 de Julio de 2026</t>
+          <t>18 de Julio de 2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -824,16 +824,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9-14-17-32-35</t>
+          <t>8-14-16-32-39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10-11-15-21-34</t>
+          <t>5-6-31-32-34</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11 de Julio de 2026</t>
+          <t>15 de Julio de 2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10-14-15-35-37</t>
+          <t>6-17-26-31-35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3-22-28-32-34</t>
+          <t>2-4-8-12-24</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -884,7 +884,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11 de Julio de 2026</t>
+          <t>15 de Julio de 2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4-12-22-28-37</t>
+          <t>4-13-17-38-40</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>29-35-38-41-42</t>
+          <t>10-22-27-30-35</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8 de Julio de 2026</t>
+          <t>13 de Julio de 2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -929,16 +929,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10-14-15-35-37</t>
+          <t>4-13-18-29-40</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11-15-20-24-30</t>
+          <t>8-11-21-32-38</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8 de Julio de 2026</t>
+          <t>13 de Julio de 2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -964,16 +964,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9-14-17-32-35</t>
+          <t>6-17-26-31-35</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4-12-26-35-37</t>
+          <t>10-11-15-21-34</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6 de Julio de 2026</t>
+          <t>11 de Julio de 2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10-14-15-35-38</t>
+          <t>4-8-12-35-38</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2-12-16-27-28</t>
+          <t>3-22-28-32-34</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6 de Julio de 2026</t>
+          <t>11 de Julio de 2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3-13-22-28-37</t>
+          <t>9-11-14-32-39</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>14-17-31-42-43</t>
+          <t>29-35-38-41-42</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4 de Julio de 2026</t>
+          <t>8 de Julio de 2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1069,16 +1069,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8-14-16-31-35</t>
+          <t>9-14-16-33-39</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>9-14-40-42-43</t>
+          <t>11-15-20-24-30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4 de Julio de 2026</t>
+          <t>8 de Julio de 2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1104,16 +1104,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11-14-15-34-37</t>
+          <t>9-14-16-33-39</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3-4-14-26-41</t>
+          <t>4-12-26-35-37</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1 de Julio de 2026</t>
+          <t>6 de Julio de 2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1139,16 +1139,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6-19-22-28-35</t>
+          <t>9-14-16-32-39</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3-12-13-17-37</t>
+          <t>2-12-16-27-28</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1 de Julio de 2026</t>
+          <t>6 de Julio de 2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1174,20 +1174,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>9-14-17-31-35</t>
+          <t>9-14-16-32-39</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3-14-26-34-35</t>
+          <t>14-17-31-42-43</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>29 de Junio de 2026</t>
+          <t>4 de Julio de 2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1209,20 +1209,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>9-14-17-31-35</t>
+          <t>9-11-14-32-38</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10-15-22-24-30</t>
+          <t>9-14-40-42-43</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>29 de Junio de 2026</t>
+          <t>4 de Julio de 2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1244,20 +1244,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11-14-15-35-37</t>
+          <t>9-11-14-32-38</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15-21-25-31-35</t>
+          <t>3-4-14-26-41</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>27 de Junio de 2026</t>
+          <t>1 de Julio de 2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1279,12 +1279,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>11-14-15-35-37</t>
+          <t>9-15-17-32-38</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>15-23-29-33-41</t>
+          <t>3-12-13-17-37</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>27 de Junio de 2026</t>
+          <t>1 de Julio de 2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1314,20 +1314,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7-19-22-28-35</t>
+          <t>4-14-34-35-37</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13-17-18-30-35</t>
+          <t>3-14-26-34-35</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>24 de Junio de 2026</t>
+          <t>29 de Junio de 2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7-19-22-28-35</t>
+          <t>4-14-34-35-37</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12-14-30-36-43</t>
+          <t>10-15-22-24-30</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>24 de Junio de 2026</t>
+          <t>29 de Junio de 2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1384,16 +1384,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7-19-22-28-35</t>
+          <t>7-17-26-31-32</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>8-17-31-36-41</t>
+          <t>15-21-25-31-35</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>22 de Junio de 2026</t>
+          <t>27 de Junio de 2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1419,20 +1419,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4-8-16-31-37</t>
+          <t>9-14-17-32-38</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>8-12-16-28-33</t>
+          <t>15-23-29-33-41</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>22 de Junio de 2026</t>
+          <t>27 de Junio de 2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4-8-15-31-37</t>
+          <t>8-14-17-32-38</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4-10-20-27-36</t>
+          <t>13-17-18-30-35</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20 de Junio de 2026</t>
+          <t>24 de Junio de 2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10-13-14-35-37</t>
+          <t>8-11-14-32-38</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>31-34-37-38-43</t>
+          <t>12-14-30-36-43</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20 de Junio de 2026</t>
+          <t>24 de Junio de 2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1524,16 +1524,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6-19-22-28-35</t>
+          <t>8-11-14-32-39</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>8-17-26-29-32</t>
+          <t>8-17-31-36-41</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17 de Junio de 2026</t>
+          <t>22 de Junio de 2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1559,16 +1559,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8-13-16-31-35</t>
+          <t>4-13-34-35-38</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16-20-34-37-39</t>
+          <t>8-12-16-28-33</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17 de Junio de 2026</t>
+          <t>22 de Junio de 2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4-8-15-31-37</t>
+          <t>8-9-14-32-39</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>7-12-19-34-35</t>
+          <t>4-10-20-27-36</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15 de Junio de 2026</t>
+          <t>20 de Junio de 2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1629,20 +1629,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4-8-15-31-37</t>
+          <t>8-10-14-32-39</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>4-13-16-22-31</t>
+          <t>31-34-37-38-43</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15 de Junio de 2026</t>
+          <t>20 de Junio de 2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1664,20 +1664,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6-19-22-28-35</t>
+          <t>8-10-14-32-39</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18-24-32-37-39</t>
+          <t>8-17-26-29-32</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13 de Junio de 2026</t>
+          <t>17 de Junio de 2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1699,20 +1699,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>9-13-14-35-37</t>
+          <t>8-14-16-32-39</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>13-18-26-28-29</t>
+          <t>16-20-34-37-39</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13 de Junio de 2026</t>
+          <t>17 de Junio de 2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1734,16 +1734,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8-13-15-30-35</t>
+          <t>8-14-16-32-39</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>22-35-37-38-42</t>
+          <t>7-12-19-34-35</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10 de Junio de 2026</t>
+          <t>15 de Junio de 2026</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8-13-15-30-35</t>
+          <t>8-9-14-32-39</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3-5-17-18-27</t>
+          <t>4-13-16-22-31</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10 de Junio de 2026</t>
+          <t>15 de Junio de 2026</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1804,20 +1804,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8-13-15-29-35</t>
+          <t>8-9-14-32-39</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7-14-22-35-41</t>
+          <t>18-24-32-37-39</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>8 de Junio de 2026</t>
+          <t>13 de Junio de 2026</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1839,20 +1839,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>9-13-14-32-37</t>
+          <t>8-9-13-32-39</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6-8-9-32-40</t>
+          <t>13-18-26-28-29</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>8 de Junio de 2026</t>
+          <t>13 de Junio de 2026</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1874,16 +1874,16 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>9-13-14-32-36</t>
+          <t>8-14-15-32-39</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>14-26-30-37-39</t>
+          <t>22-35-37-38-42</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6 de Junio de 2026</t>
+          <t>10 de Junio de 2026</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1909,16 +1909,16 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>9-13-32-35-37</t>
+          <t>8-13-15-32-39</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>5-15-19-28-32</t>
+          <t>3-5-17-18-27</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6 de Junio de 2026</t>
+          <t>10 de Junio de 2026</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1944,16 +1944,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>9-13-14-32-37</t>
+          <t>6-15-23-28-29</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>7-11-25-32-36</t>
+          <t>7-14-22-35-41</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3 de Junio de 2026</t>
+          <t>8 de Junio de 2026</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1979,16 +1979,16 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>9-13-14-32-36</t>
+          <t>6-15-24-28-29</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>26-29-35-38-41</t>
+          <t>6-8-9-32-40</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3 de Junio de 2026</t>
+          <t>8 de Junio de 2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2014,16 +2014,16 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>9-13-14-32-37</t>
+          <t>5-15-24-28-29</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>4-12-13-31-35</t>
+          <t>14-26-30-37-39</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1 de Junio de 2026</t>
+          <t>6 de Junio de 2026</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2049,16 +2049,16 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>9-13-14-32-37</t>
+          <t>4-13-32-34-37</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4-22-30-31-39</t>
+          <t>5-15-19-28-32</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1 de Junio de 2026</t>
+          <t>6 de Junio de 2026</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2084,16 +2084,16 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>9-13-14-32-37</t>
+          <t>4-13-32-35-37</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>12-19-33-35-41</t>
+          <t>7-11-25-32-36</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>30 de Mayo de 2026</t>
+          <t>3 de Junio de 2026</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>9-13-14-32-37</t>
+          <t>4-6-31-36-42</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2-8-11-25-26</t>
+          <t>26-29-35-38-41</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>30 de Mayo de 2026</t>
+          <t>3 de Junio de 2026</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2154,16 +2154,16 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>9-13-14-32-37</t>
+          <t>5-15-24-28-29</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>8-14-23-34-38</t>
+          <t>4-12-13-31-35</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>27 de Mayo de 2026</t>
+          <t>1 de Junio de 2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>9-13-14-32-37</t>
+          <t>4-13-32-35-38</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>7-14-20-23-40</t>
+          <t>4-22-30-31-39</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>27 de Mayo de 2026</t>
+          <t>1 de Junio de 2026</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2224,16 +2224,16 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>9-13-14-32-37</t>
+          <t>5-15-24-28-29</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>11-24-26-31-37</t>
+          <t>12-19-33-35-41</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>25 de Mayo de 2026</t>
+          <t>30 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2259,20 +2259,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>9-13-14-32-37</t>
+          <t>4-13-32-34-37</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>12-14-37-38-39</t>
+          <t>2-8-11-25-26</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>25 de Mayo de 2026</t>
+          <t>30 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2294,20 +2294,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>9-13-14-32-37</t>
+          <t>4-13-32-34-37</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>6-13-20-32-42</t>
+          <t>8-14-23-34-38</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>23 de Mayo de 2026</t>
+          <t>27 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2329,12 +2329,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>9-13-14-32-37</t>
+          <t>5-15-24-28-29</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>23-27-29-30-38</t>
+          <t>7-14-20-23-40</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>23 de Mayo de 2026</t>
+          <t>27 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>9-13-14-32-37</t>
+          <t>4-13-32-34-37</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>12-16-25-27-37</t>
+          <t>11-24-26-31-37</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20 de Mayo de 2026</t>
+          <t>25 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>6-12-15-28-34</t>
+          <t>4-13-32-35-37</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1-28-32-33-35</t>
+          <t>12-14-37-38-39</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20 de Mayo de 2026</t>
+          <t>25 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>9-13-14-32-37</t>
+          <t>5-15-24-28-29</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>4-8-10-42-43</t>
+          <t>6-13-20-32-42</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>14 de Julio de 2026</t>
+          <t>21 de Julio de 2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2469,16 +2469,16 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>3-5-23-26-37</t>
+          <t>3-15-26-29-36</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>8-13-22-23-31</t>
+          <t>6-16-21-30-32</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>13 de Julio de 2026</t>
+          <t>20 de Julio de 2026</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3-5-24-26-37</t>
+          <t>3-15-26-29-37</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>13-18-25-32-33</t>
+          <t>8-9-13-18-34</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10 de Julio de 2026</t>
+          <t>17 de Julio de 2026</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2539,16 +2539,16 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>11-15-22-26-27</t>
+          <t>3-15-26-29-37</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>16-18-32-34-36</t>
+          <t>8-22-25-26-32</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>9 de Julio de 2026</t>
+          <t>16 de Julio de 2026</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3-19-21-26-27</t>
+          <t>3-15-26-29-36</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>4-13-26-34-39</t>
+          <t>4-17-18-36-37</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>7 de Julio de 2026</t>
+          <t>14 de Julio de 2026</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>11-14-22-26-27</t>
+          <t>3-15-26-29-37</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1-13-21-29-33</t>
+          <t>8-13-22-23-31</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>6 de Julio de 2026</t>
+          <t>13 de Julio de 2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>5-12-15-26-35</t>
+          <t>3-15-26-29-37</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2-17-26-28-30</t>
+          <t>13-18-25-32-33</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3 de Julio de 2026</t>
+          <t>10 de Julio de 2026</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2679,16 +2679,16 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>5-12-15-25-35</t>
+          <t>3-15-26-29-37</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>17-21-27-32-35</t>
+          <t>16-18-32-34-36</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2 de Julio de 2026</t>
+          <t>9 de Julio de 2026</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>5-12-15-26-36</t>
+          <t>3-15-26-29-37</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>10-12-16-19-32</t>
+          <t>4-13-26-34-39</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30 de Junio de 2026</t>
+          <t>7 de Julio de 2026</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2749,16 +2749,16 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5-11-14-26-36</t>
+          <t>3-15-26-29-37</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>3-12-29-32-39</t>
+          <t>1-13-21-29-33</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>29 de Junio de 2026</t>
+          <t>6 de Julio de 2026</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2784,16 +2784,16 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>5-13-15-26-35</t>
+          <t>3-15-26-29-37</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2-4-20-32-37</t>
+          <t>2-17-26-28-30</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>26 de Junio de 2026</t>
+          <t>3 de Julio de 2026</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>5-12-15-25-35</t>
+          <t>3-15-26-29-37</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>21-29-32-36-38</t>
+          <t>17-21-27-32-35</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>25 de Junio de 2026</t>
+          <t>2 de Julio de 2026</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2854,16 +2854,16 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2-5-23-25-37</t>
+          <t>3-15-26-30-37</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>3-15-25-30-35</t>
+          <t>10-12-16-19-32</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>23 de Junio de 2026</t>
+          <t>30 de Junio de 2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3-7-24-26-37</t>
+          <t>3-15-26-29-37</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>3-5-7-34-38</t>
+          <t>3-12-29-32-39</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>22 de Junio de 2026</t>
+          <t>29 de Junio de 2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2924,16 +2924,16 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3-7-24-26-37</t>
+          <t>1-10-11-32-36</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>4-12-22-30-31</t>
+          <t>2-4-20-32-37</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>19 de Junio de 2026</t>
+          <t>26 de Junio de 2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3-19-21-26-27</t>
+          <t>3-15-26-30-37</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2-22-35-36-37</t>
+          <t>21-29-32-36-38</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>18 de Junio de 2026</t>
+          <t>25 de Junio de 2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2994,20 +2994,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>3-7-23-26-37</t>
+          <t>3-15-27-30-37</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>6-7-11-14-21</t>
+          <t>3-15-25-30-35</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>16 de Junio de 2026</t>
+          <t>23 de Junio de 2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3029,16 +3029,16 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3-7-24-26-37</t>
+          <t>3-16-26-29-37</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>6-16-27-30-34</t>
+          <t>3-5-7-34-38</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15 de Junio de 2026</t>
+          <t>22 de Junio de 2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>12-15-22-26-27</t>
+          <t>3-15-26-29-37</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>11-16-28-33-38</t>
+          <t>4-12-22-30-31</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>12 de Junio de 2026</t>
+          <t>19 de Junio de 2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3099,20 +3099,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>12-15-22-26-27</t>
+          <t>3-16-26-29-37</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1-15-18-22-29</t>
+          <t>2-22-35-36-37</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>11 de Junio de 2026</t>
+          <t>18 de Junio de 2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3134,20 +3134,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>12-15-22-26-27</t>
+          <t>3-16-26-29-37</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>19-23-26-27-36</t>
+          <t>6-7-11-14-21</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>9 de Junio de 2026</t>
+          <t>16 de Junio de 2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>12-15-22-26-27</t>
+          <t>3-16-26-29-37</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>6-10-14-17-27</t>
+          <t>6-16-27-30-34</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>8 de Junio de 2026</t>
+          <t>15 de Junio de 2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3204,16 +3204,16 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>12-15-22-26-27</t>
+          <t>3-16-26-29-37</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>9-13-18-29-32</t>
+          <t>11-16-28-33-38</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5 de Junio de 2026</t>
+          <t>12 de Junio de 2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3239,20 +3239,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>8-10-13-17-35</t>
+          <t>3-15-26-29-37</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2-14-22-36-38</t>
+          <t>1-15-18-22-29</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>4 de Junio de 2026</t>
+          <t>11 de Junio de 2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>12-15-22-26-27</t>
+          <t>3-15-26-29-37</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>3-7-12-17-36</t>
+          <t>19-23-26-27-36</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2 de Junio de 2026</t>
+          <t>9 de Junio de 2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>12-15-22-26-27</t>
+          <t>3-15-26-29-37</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>4-5-8-31-35</t>
+          <t>6-10-14-17-27</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1 de Junio de 2026</t>
+          <t>8 de Junio de 2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>12-15-22-26-27</t>
+          <t>3-15-26-29-37</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>4-8-23-26-30</t>
+          <t>9-13-18-29-32</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>29 de Mayo de 2026</t>
+          <t>5 de Junio de 2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3379,16 +3379,16 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>3-8-24-25-37</t>
+          <t>3-16-26-29-37</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>3-12-15-23-28</t>
+          <t>2-14-22-36-38</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>28 de Mayo de 2026</t>
+          <t>4 de Junio de 2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>8-11-13-16-35</t>
+          <t>3-16-26-29-37</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>5-8-15-37-38</t>
+          <t>3-7-12-17-36</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>26 de Mayo de 2026</t>
+          <t>2 de Junio de 2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3449,16 +3449,16 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>3-8-23-25-37</t>
+          <t>3-15-26-29-37</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>5-7-12-24-25</t>
+          <t>4-5-8-31-35</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>25 de Mayo de 2026</t>
+          <t>1 de Junio de 2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3484,16 +3484,16 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>12-15-22-26-27</t>
+          <t>3-15-26-29-37</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2-8-23-28-34</t>
+          <t>4-8-23-26-30</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>22 de Mayo de 2026</t>
+          <t>29 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3519,16 +3519,16 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>8-11-12-33-37</t>
+          <t>3-16-26-29-37</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1-18-19-22-35</t>
+          <t>3-12-15-23-28</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>21 de Mayo de 2026</t>
+          <t>28 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>3-8-24-26-37</t>
+          <t>3-16-26-29-37</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>3-5-31-32-38</t>
+          <t>5-8-15-37-38</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>19 de Mayo de 2026</t>
+          <t>26 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>3-7-24-26-37</t>
+          <t>3-16-26-29-37</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>8-14-19-21-38</t>
+          <t>5-7-12-24-25</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>18 de Mayo de 2026</t>
+          <t>25 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3624,16 +3624,16 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>12-15-23-27-28</t>
+          <t>3-16-26-29-37</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>5-9-12-31-34</t>
+          <t>2-8-23-28-34</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15 de Mayo de 2026</t>
+          <t>22 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3659,16 +3659,16 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>8-11-12-17-35</t>
+          <t>3-13-15-16-36</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>9-21-23-34-35</t>
+          <t>1-18-19-22-35</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>14 de Mayo de 2026</t>
+          <t>21 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3694,12 +3694,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1-8-16-29-39</t>
+          <t>3-16-26-29-37</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>11-20-25-28-29</t>
+          <t>3-5-31-32-38</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>12 de Mayo de 2026</t>
+          <t>19 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3729,20 +3729,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>1-8-16-29-39</t>
+          <t>3-16-27-29-37</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1-6-8-27-35</t>
+          <t>8-14-19-21-38</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>11 de Mayo de 2026</t>
+          <t>18 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>12-15-22-26-27</t>
+          <t>3-15-26-29-37</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>3-7-8-35-38</t>
+          <t>5-9-12-31-34</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>8 de Mayo de 2026</t>
+          <t>15 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3799,16 +3799,16 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>3-9-13-26-33</t>
+          <t>3-15-26-29-37</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1-2-13-28-31</t>
+          <t>9-21-23-34-35</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>7 de Mayo de 2026</t>
+          <t>14 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>9-10-11-33-37</t>
+          <t>3-15-26-29-37</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>25-29-34-37-39</t>
+          <t>11-20-25-28-29</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5 de Mayo de 2026</t>
+          <t>12 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3869,20 +3869,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>3-16-25-33-37</t>
+          <t>3-15-26-29-37</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>4-24-33-35-37</t>
+          <t>1-6-8-27-35</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✗</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>4 de Mayo de 2026</t>
+          <t>11 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3904,16 +3904,16 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>3-16-24-33-37</t>
+          <t>3-15-26-29-37</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>5-10-20-25-27</t>
+          <t>3-7-8-35-38</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1 de Mayo de 2026</t>
+          <t>8 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3939,16 +3939,16 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>8-11-13-17-35</t>
+          <t>3-16-27-30-37</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>3-13-15-33-37</t>
+          <t>1-2-13-28-31</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>30 de Abril de 2026</t>
+          <t>7 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3974,20 +3974,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>3-8-23-25-37</t>
+          <t>3-15-26-29-37</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>13-20-32-35-36</t>
+          <t>25-29-34-37-39</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>28 de Abril de 2026</t>
+          <t>5 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>3-8-23-24-36</t>
+          <t>3-16-26-29-37</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>8-16-26-37-38</t>
+          <t>4-24-33-35-37</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>27 de Abril de 2026</t>
+          <t>4 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4044,16 +4044,16 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>3-8-23-25-36</t>
+          <t>3-15-26-29-37</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>6-15-17-25-38</t>
+          <t>5-10-20-25-27</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>24 de Abril de 2026</t>
+          <t>1 de Mayo de 2026</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4079,20 +4079,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>8-11-12-17-34</t>
+          <t>3-16-26-29-37</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>20-25-28-32-35</t>
+          <t>3-13-15-33-37</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>23 de Abril de 2026</t>
+          <t>30 de Abril de 2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>12-15-22-26-31</t>
+          <t>3-16-26-29-37</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>3-4-8-10-30</t>
+          <t>13-20-32-35-36</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>21 de Abril de 2026</t>
+          <t>28 de Abril de 2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4149,16 +4149,16 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>12-15-22-26-31</t>
+          <t>3-15-26-29-36</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>3-4-21-23-29</t>
+          <t>8-16-26-37-38</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>20 de Abril de 2026</t>
+          <t>27 de Abril de 2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4184,16 +4184,16 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>13-15-16-26-39</t>
+          <t>3-15-26-29-36</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>4-12-27-30-35</t>
+          <t>6-15-17-25-38</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
         <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.74</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="3">
@@ -4268,16 +4268,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
         <v>50</v>
       </c>
       <c r="D3" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.74</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="4">
@@ -4296,7 +4296,7 @@
         <v>0.1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
     </row>
   </sheetData>
@@ -4310,7 +4310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5641,6 +5641,966 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:48:38</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D56" t="n">
+        <v>100</v>
+      </c>
+      <c r="E56" t="n">
+        <v>13</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:48:52</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D57" t="n">
+        <v>100</v>
+      </c>
+      <c r="E57" t="n">
+        <v>13</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>3</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:49:02</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D58" t="n">
+        <v>100</v>
+      </c>
+      <c r="E58" t="n">
+        <v>13</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>4</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:49:12</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D59" t="n">
+        <v>100</v>
+      </c>
+      <c r="E59" t="n">
+        <v>13</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>5</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:49:23</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D60" t="n">
+        <v>100</v>
+      </c>
+      <c r="E60" t="n">
+        <v>13</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>6</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:49:34</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D61" t="n">
+        <v>100</v>
+      </c>
+      <c r="E61" t="n">
+        <v>13</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>7</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:49:45</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D62" t="n">
+        <v>100</v>
+      </c>
+      <c r="E62" t="n">
+        <v>13</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>8</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:49:56</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D63" t="n">
+        <v>100</v>
+      </c>
+      <c r="E63" t="n">
+        <v>13</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>9</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:50:06</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D64" t="n">
+        <v>100</v>
+      </c>
+      <c r="E64" t="n">
+        <v>13</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>10</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:50:17</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D65" t="n">
+        <v>100</v>
+      </c>
+      <c r="E65" t="n">
+        <v>13</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>1</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:53:58</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D66" t="n">
+        <v>100</v>
+      </c>
+      <c r="E66" t="n">
+        <v>13</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:54:15</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D67" t="n">
+        <v>100</v>
+      </c>
+      <c r="E67" t="n">
+        <v>13</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>3</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:54:26</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D68" t="n">
+        <v>100</v>
+      </c>
+      <c r="E68" t="n">
+        <v>13</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>4</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:54:36</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D69" t="n">
+        <v>100</v>
+      </c>
+      <c r="E69" t="n">
+        <v>13</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>5</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:54:46</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D70" t="n">
+        <v>100</v>
+      </c>
+      <c r="E70" t="n">
+        <v>13</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>6</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:54:56</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D71" t="n">
+        <v>100</v>
+      </c>
+      <c r="E71" t="n">
+        <v>13</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>7</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:55:07</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D72" t="n">
+        <v>100</v>
+      </c>
+      <c r="E72" t="n">
+        <v>13</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>8</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:55:17</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D73" t="n">
+        <v>100</v>
+      </c>
+      <c r="E73" t="n">
+        <v>13</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>9</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:55:26</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D74" t="n">
+        <v>100</v>
+      </c>
+      <c r="E74" t="n">
+        <v>13</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>10</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:55:36</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D75" t="n">
+        <v>100</v>
+      </c>
+      <c r="E75" t="n">
+        <v>13</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>1</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:42:36</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D76" t="n">
+        <v>100</v>
+      </c>
+      <c r="E76" t="n">
+        <v>10</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:42:59</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D77" t="n">
+        <v>100</v>
+      </c>
+      <c r="E77" t="n">
+        <v>10</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>3</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:43:10</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D78" t="n">
+        <v>100</v>
+      </c>
+      <c r="E78" t="n">
+        <v>10</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>4</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:43:21</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D79" t="n">
+        <v>100</v>
+      </c>
+      <c r="E79" t="n">
+        <v>10</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>5</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:43:34</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>100</v>
+      </c>
+      <c r="E80" t="n">
+        <v>10</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>6</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:43:47</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D81" t="n">
+        <v>100</v>
+      </c>
+      <c r="E81" t="n">
+        <v>10</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>7</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:43:58</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D82" t="n">
+        <v>100</v>
+      </c>
+      <c r="E82" t="n">
+        <v>10</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>8</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:44:08</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D83" t="n">
+        <v>100</v>
+      </c>
+      <c r="E83" t="n">
+        <v>10</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>9</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:44:19</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D84" t="n">
+        <v>100</v>
+      </c>
+      <c r="E84" t="n">
+        <v>10</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>10</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:44:29</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D85" t="n">
+        <v>100</v>
+      </c>
+      <c r="E85" t="n">
+        <v>10</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>1</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:50:07</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D86" t="n">
+        <v>100</v>
+      </c>
+      <c r="E86" t="n">
+        <v>10</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>2</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:50:20</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D87" t="n">
+        <v>100</v>
+      </c>
+      <c r="E87" t="n">
+        <v>10</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>3</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:50:35</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D88" t="n">
+        <v>100</v>
+      </c>
+      <c r="E88" t="n">
+        <v>10</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>4</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:50:57</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D89" t="n">
+        <v>100</v>
+      </c>
+      <c r="E89" t="n">
+        <v>10</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>5</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:51:17</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D90" t="n">
+        <v>100</v>
+      </c>
+      <c r="E90" t="n">
+        <v>10</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>6</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:51:29</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D91" t="n">
+        <v>100</v>
+      </c>
+      <c r="E91" t="n">
+        <v>10</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>7</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:51:47</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D92" t="n">
+        <v>100</v>
+      </c>
+      <c r="E92" t="n">
+        <v>10</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>8</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:51:58</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D93" t="n">
+        <v>100</v>
+      </c>
+      <c r="E93" t="n">
+        <v>10</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>9</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:52:09</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D94" t="n">
+        <v>100</v>
+      </c>
+      <c r="E94" t="n">
+        <v>10</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>10</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-07-22 19:52:20</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D95" t="n">
+        <v>100</v>
+      </c>
+      <c r="E95" t="n">
+        <v>10</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
